--- a/threshold_eval.xlsx
+++ b/threshold_eval.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -546,8 +546,11 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="55" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -612,10 +615,25 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Precision (ngưỡng tối ưu)</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Recall (ngưỡng tối ưu)</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
           <t>F1 nếu luôn dự đoán "có bệnh"</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
@@ -654,9 +672,18 @@
         <v>0.3810302534750613</v>
       </c>
       <c r="J5" s="7" t="n">
+        <v>0.3248513108041403</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>0.2900715841892312</v>
+      </c>
+      <c r="L5" s="7" t="n">
+        <v>0.5550923168552709</v>
+      </c>
+      <c r="M5" s="7" t="n">
         <v>0.2720570363768938</v>
       </c>
-      <c r="K5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -691,9 +718,18 @@
         <v>0.5522570150467669</v>
       </c>
       <c r="J6" s="7" t="n">
+        <v>0.5340887162584922</v>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>0.4718554551772064</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>0.6656862745098039</v>
+      </c>
+      <c r="M6" s="7" t="n">
         <v>0.1745977404998288</v>
       </c>
-      <c r="K6" s="8" t="inlineStr"/>
+      <c r="N6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -728,9 +764,18 @@
         <v>0.371630029033596</v>
       </c>
       <c r="J7" s="7" t="n">
+        <v>0.2967124925545567</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>0.3093922651933702</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <v>0.4652128764278297</v>
+      </c>
+      <c r="M7" s="7" t="n">
         <v>0.165648920615808</v>
       </c>
-      <c r="K7" s="8" t="inlineStr"/>
+      <c r="N7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -765,9 +810,18 @@
         <v>0.2772727272727273</v>
       </c>
       <c r="J8" s="7" t="n">
+        <v>0.1934908269850908</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>0.2392156862745098</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>0.3297297297297297</v>
+      </c>
+      <c r="M8" s="7" t="n">
         <v>0.09893929940279883</v>
       </c>
-      <c r="K8" s="8" t="inlineStr"/>
+      <c r="N8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -802,9 +856,18 @@
         <v>0.3682076236820763</v>
       </c>
       <c r="J9" s="7" t="n">
+        <v>0.2990766801633375</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <v>0.3135359116022099</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <v>0.4459724950884086</v>
+      </c>
+      <c r="M9" s="7" t="n">
         <v>0.09111250335630539</v>
       </c>
-      <c r="K9" s="8" t="inlineStr"/>
+      <c r="N9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -839,9 +902,18 @@
         <v>0.2297772567409144</v>
       </c>
       <c r="J10" s="7" t="n">
+        <v>0.1439456983941278</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>0.2024793388429752</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>0.2655826558265583</v>
+      </c>
+      <c r="M10" s="7" t="n">
         <v>0.06689023837578176</v>
       </c>
-      <c r="K10" s="8" t="inlineStr"/>
+      <c r="N10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -876,9 +948,18 @@
         <v>0.3337713534822602</v>
       </c>
       <c r="J11" s="7" t="n">
+        <v>0.2318790619562635</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>0.2892938496583143</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>0.3944099378881988</v>
+      </c>
+      <c r="M11" s="7" t="n">
         <v>0.05862006189695977</v>
       </c>
-      <c r="K11" s="8" t="inlineStr"/>
+      <c r="N11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -913,9 +994,18 @@
         <v>0.242837653478854</v>
       </c>
       <c r="J12" s="7" t="n">
+        <v>0.1529503062913224</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>0.1951754385964912</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>0.3212996389891697</v>
+      </c>
+      <c r="M12" s="7" t="n">
         <v>0.05063522529933278</v>
       </c>
-      <c r="K12" s="8" t="inlineStr"/>
+      <c r="N12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -950,9 +1040,18 @@
         <v>0.3063829787234043</v>
       </c>
       <c r="J13" s="7" t="n">
+        <v>0.2084763342972624</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>0.2676579925650557</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>0.3582089552238806</v>
+      </c>
+      <c r="M13" s="7" t="n">
         <v>0.03699953980671882</v>
       </c>
-      <c r="K13" s="8" t="inlineStr"/>
+      <c r="N13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -987,9 +1086,18 @@
         <v>0.3701657458563536</v>
       </c>
       <c r="J14" s="7" t="n">
+        <v>0.2838750376036453</v>
+      </c>
+      <c r="K14" s="7" t="n">
+        <v>0.3435897435897436</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>0.4011976047904192</v>
+      </c>
+      <c r="M14" s="7" t="n">
         <v>0.03083741113470594</v>
       </c>
-      <c r="K14" s="8" t="inlineStr"/>
+      <c r="N14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1024,9 +1132,18 @@
         <v>0.1743869209809264</v>
       </c>
       <c r="J15" s="7" t="n">
+        <v>0.08553625041949939</v>
+      </c>
+      <c r="K15" s="7" t="n">
+        <v>0.1488372093023256</v>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>0.2105263157894737</v>
+      </c>
+      <c r="M15" s="7" t="n">
         <v>0.02810650887573964</v>
       </c>
-      <c r="K15" s="8" t="inlineStr"/>
+      <c r="N15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1061,9 +1178,18 @@
         <v>0.2863340563991323</v>
       </c>
       <c r="J16" s="7" t="n">
+        <v>0.1635185584846966</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>0.2129032258064516</v>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>0.4370860927152318</v>
+      </c>
+      <c r="M16" s="7" t="n">
         <v>0.02792417938049006</v>
       </c>
-      <c r="K16" s="8" t="inlineStr"/>
+      <c r="N16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1098,9 +1224,18 @@
         <v>0.1087378640776699</v>
       </c>
       <c r="J17" s="7" t="n">
+        <v>0.03976701698369071</v>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>0.2434782608695652</v>
+      </c>
+      <c r="M17" s="7" t="n">
         <v>0.02133778643658966</v>
       </c>
-      <c r="K17" s="8" t="inlineStr">
+      <c r="N17" s="8" t="inlineStr">
         <is>
           <t>Ít ca dương (&lt;150): CI tương đối rộng.</t>
         </is>
@@ -1139,9 +1274,18 @@
         <v>0.1875</v>
       </c>
       <c r="J18" s="12" t="n">
+        <v>0.1178356091652405</v>
+      </c>
+      <c r="K18" s="12" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="L18" s="12" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="M18" s="12" t="n">
         <v>0.003370155401610185</v>
       </c>
-      <c r="K18" s="13" t="inlineStr">
+      <c r="N18" s="13" t="inlineStr">
         <is>
           <t>CHỈ 18 ca dương trong val: CI rất rộng, ngưỡng tối ưu và F1 không đáng tin (F1 có thể bị thổi phồng).</t>
         </is>
@@ -1173,20 +1317,29 @@
       <c r="I19" s="16" t="n">
         <v>0.2993065341606959</v>
       </c>
-      <c r="J19" s="15" t="n"/>
-      <c r="K19" s="15" t="n"/>
+      <c r="J19" s="16" t="n">
+        <v>0.2197145643115261</v>
+      </c>
+      <c r="K19" s="16" t="n">
+        <v>0.2548781010774</v>
+      </c>
+      <c r="L19" s="16" t="n">
+        <v>0.3757249872407291</v>
+      </c>
+      <c r="M19" s="15" t="n"/>
+      <c r="N19" s="15" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Tô cam = bệnh dưới 50 ca dương. Hernia chỉ 18 ca dương nên mọi số liệu của bệnh này chỉ mang tính tham khảo. Cột "F1 nếu luôn dự đoán có bệnh" = 2π/(1+π), mức nền để so với F1 của mô hình.</t>
+          <t>Tô cam = bệnh dưới 50 ca dương. Hernia chỉ 18 ca dương nên mọi số liệu của bệnh này chỉ mang tính tham khảo. Cột "F1 nếu luôn dự đoán có bệnh" = 2π/(1+π), mức nền để so với F1 của mô hình. AP của mô hình không có kỹ năng bằng đúng tỉ lệ bệnh (cột 2), nên AP bệnh hiếm phải so với số rất nhỏ. Precision/Recall tính tại ngưỡng tối ưu (chọn trên val).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A21:K21"/>
+    <mergeCell ref="A21:N21"/>
+    <mergeCell ref="A2:N2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
